--- a/Project File.xlsx
+++ b/Project File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Siddharth's File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98422F23-E8BF-41C6-819A-259763E118D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD6174D-95C8-4FC1-9229-1DC4E3762540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>Waiting for the weekend.</t>
+  </si>
+  <si>
+    <t>Learnt new Sql Query techniques.</t>
   </si>
 </sst>
 </file>
@@ -1835,27 +1838,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B23" s="14">
+        <v>460</v>
+      </c>
+      <c r="C23" s="14">
+        <v>45</v>
+      </c>
+      <c r="D23" s="14">
+        <v>335</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>180</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" ref="I23" si="6">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <v>1440</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" ref="J23" si="7">IF(I23="","",1440-I23)</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
@@ -2879,11 +2906,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2901,11 +2928,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2923,11 +2950,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2945,11 +2972,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2967,11 +2994,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2989,11 +3016,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3011,11 +3038,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3033,11 +3060,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3055,11 +3082,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3077,11 +3104,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3099,11 +3126,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3121,11 +3148,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3143,11 +3170,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3165,11 +3192,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3187,11 +3214,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3209,11 +3236,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3231,11 +3258,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3253,11 +3280,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3275,11 +3302,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3297,11 +3324,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3319,11 +3346,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3341,11 +3368,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3363,11 +3390,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3385,11 +3412,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3407,11 +3434,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3429,11 +3456,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3451,11 +3478,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3473,11 +3500,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3495,11 +3522,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3517,11 +3544,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3539,11 +3566,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3561,11 +3588,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3583,11 +3610,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3605,11 +3632,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3627,11 +3654,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3649,11 +3676,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3671,11 +3698,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3693,11 +3720,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3715,11 +3742,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3737,11 +3764,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3759,11 +3786,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3781,11 +3808,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3803,11 +3830,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3825,11 +3852,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3847,11 +3874,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3869,11 +3896,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3891,11 +3918,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3913,11 +3940,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3935,11 +3962,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3957,11 +3984,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3979,11 +4006,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4001,11 +4028,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4023,11 +4050,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4045,11 +4072,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4067,11 +4094,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4089,11 +4116,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4111,11 +4138,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4133,11 +4160,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4155,11 +4182,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4177,11 +4204,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4199,11 +4226,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4221,11 +4248,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4243,11 +4270,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4265,11 +4292,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4287,11 +4314,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4309,11 +4336,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4331,11 +4358,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4353,11 +4380,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4375,11 +4402,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4397,11 +4424,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4419,11 +4446,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4441,11 +4468,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4463,11 +4490,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4485,11 +4512,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4507,11 +4534,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4529,11 +4556,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4551,11 +4578,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4573,11 +4600,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4595,11 +4622,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4617,11 +4644,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4639,11 +4666,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4661,11 +4688,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4683,11 +4710,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4705,11 +4732,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4727,11 +4754,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4749,11 +4776,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4771,11 +4798,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4793,11 +4820,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4815,11 +4842,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4837,11 +4864,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4859,11 +4886,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4881,11 +4908,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4903,11 +4930,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4925,11 +4952,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4947,11 +4974,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4969,11 +4996,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4991,11 +5018,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5013,11 +5040,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5035,11 +5062,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5057,11 +5084,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5079,11 +5106,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5101,11 +5128,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5123,11 +5150,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5145,11 +5172,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5167,11 +5194,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5189,11 +5216,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5211,11 +5238,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5233,11 +5260,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5255,11 +5282,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5277,11 +5304,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5299,11 +5326,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5321,11 +5348,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5343,11 +5370,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5365,11 +5392,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5387,11 +5414,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5409,11 +5436,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5431,11 +5458,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5453,11 +5480,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5475,11 +5502,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5497,11 +5524,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5519,11 +5546,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5541,11 +5568,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5563,11 +5590,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5585,11 +5612,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5607,11 +5634,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5629,11 +5656,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5651,11 +5678,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5673,11 +5700,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5695,11 +5722,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5717,11 +5744,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5739,11 +5766,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5761,11 +5788,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5783,11 +5810,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5805,11 +5832,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5827,11 +5854,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5849,11 +5876,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5871,11 +5898,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5893,11 +5920,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5915,11 +5942,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5937,11 +5964,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5959,11 +5986,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5981,11 +6008,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6003,11 +6030,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6025,11 +6052,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6047,11 +6074,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6069,11 +6096,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6091,11 +6118,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6113,11 +6140,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6135,11 +6162,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6157,11 +6184,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6179,11 +6206,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6201,11 +6228,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6223,11 +6250,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6245,11 +6272,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6267,11 +6294,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6289,11 +6316,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6311,11 +6338,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6333,11 +6360,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6355,11 +6382,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6377,11 +6404,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6399,11 +6426,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6421,11 +6448,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6443,11 +6470,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6465,11 +6492,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6487,11 +6514,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6509,11 +6536,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6531,11 +6558,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6553,11 +6580,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6575,11 +6602,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6597,11 +6624,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6619,11 +6646,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6641,11 +6668,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6663,11 +6690,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6685,11 +6712,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6707,11 +6734,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6729,11 +6756,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6751,11 +6778,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6773,11 +6800,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6795,11 +6822,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6817,11 +6844,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6839,11 +6866,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6861,11 +6888,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6883,11 +6910,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6905,11 +6932,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6927,11 +6954,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6949,11 +6976,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6971,11 +6998,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6993,11 +7020,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7015,11 +7042,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7037,11 +7064,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7059,11 +7086,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7081,11 +7108,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7103,11 +7130,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7125,11 +7152,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7147,11 +7174,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7169,11 +7196,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7191,11 +7218,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7213,11 +7240,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7235,11 +7262,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7257,11 +7284,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7279,11 +7306,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7301,11 +7328,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7323,11 +7350,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7345,11 +7372,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7367,11 +7394,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7389,11 +7416,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7411,11 +7438,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7433,11 +7460,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7455,11 +7482,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7477,11 +7504,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7499,11 +7526,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7521,11 +7548,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7543,11 +7570,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7565,11 +7592,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7587,11 +7614,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7609,11 +7636,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7631,11 +7658,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7653,11 +7680,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7675,11 +7702,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7697,11 +7724,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7719,11 +7746,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7741,11 +7768,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7763,11 +7790,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7785,11 +7812,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7807,11 +7834,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7829,11 +7856,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7851,11 +7878,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7873,11 +7900,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7895,11 +7922,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7917,11 +7944,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7939,11 +7966,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7961,11 +7988,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7983,11 +8010,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8005,11 +8032,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8027,11 +8054,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8049,11 +8076,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8071,11 +8098,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8093,11 +8120,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8115,11 +8142,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8137,11 +8164,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8159,11 +8186,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8181,11 +8208,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8203,11 +8230,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8225,11 +8252,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8247,11 +8274,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8269,11 +8296,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8291,11 +8318,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8313,11 +8340,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8335,11 +8362,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8357,11 +8384,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8379,11 +8406,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8401,11 +8428,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8423,11 +8450,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8445,11 +8472,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8467,11 +8494,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8489,11 +8516,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8511,11 +8538,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8533,11 +8560,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8555,11 +8582,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8577,11 +8604,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8599,11 +8626,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8621,11 +8648,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8643,11 +8670,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8665,11 +8692,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8687,11 +8714,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8709,11 +8736,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8731,11 +8758,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8753,11 +8780,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8775,11 +8802,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8797,11 +8824,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8819,11 +8846,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8841,11 +8868,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8863,11 +8890,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8885,11 +8912,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8907,11 +8934,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8929,11 +8956,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8951,11 +8978,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8973,11 +9000,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8995,11 +9022,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9017,11 +9044,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9039,11 +9066,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9061,11 +9088,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9083,11 +9110,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9105,11 +9132,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9127,11 +9154,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9149,11 +9176,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9171,11 +9198,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9193,11 +9220,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9215,11 +9242,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9237,11 +9264,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9259,11 +9286,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9281,11 +9308,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9303,11 +9330,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9325,11 +9352,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9347,11 +9374,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9369,11 +9396,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9391,11 +9418,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9413,11 +9440,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9435,11 +9462,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9457,11 +9484,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9479,11 +9506,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9501,11 +9528,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9523,11 +9550,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9545,11 +9572,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9567,11 +9594,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9589,11 +9616,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9611,11 +9638,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9633,11 +9660,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9655,11 +9682,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9677,11 +9704,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9699,11 +9726,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9721,11 +9748,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9743,11 +9770,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9765,11 +9792,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9787,11 +9814,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9809,11 +9836,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9831,11 +9858,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9853,11 +9880,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9875,11 +9902,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9897,11 +9924,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9919,11 +9946,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9941,11 +9968,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9963,11 +9990,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9985,11 +10012,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10007,11 +10034,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10029,11 +10056,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10051,11 +10078,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10073,11 +10100,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10095,11 +10122,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10117,11 +10144,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10139,11 +10166,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10161,11 +10188,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/Project File.xlsx
+++ b/Project File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Siddharth's File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD6174D-95C8-4FC1-9229-1DC4E3762540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D95596-BA82-4645-8C7C-90617863D746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Learnt new Sql Query techniques.</t>
+  </si>
+  <si>
+    <t>Met an old friend.</t>
   </si>
 </sst>
 </file>
@@ -1885,26 +1888,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+      <c r="A24" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B24" s="14">
+        <v>400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>45</v>
+      </c>
+      <c r="D24" s="14">
+        <v>300</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>420</v>
+      </c>
+      <c r="G24" s="14">
+        <v>6</v>
+      </c>
+      <c r="H24" s="14">
+        <v>155</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" ref="I24" si="8">IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
+        <v>1440</v>
+      </c>
+      <c r="J24" s="15">
+        <f t="shared" ref="J24" si="9">IF(I24="","",1440-I24)</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
@@ -2906,11 +2933,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2928,11 +2955,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2950,11 +2977,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2972,11 +2999,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2994,11 +3021,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3016,11 +3043,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3038,11 +3065,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3060,11 +3087,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3082,11 +3109,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3104,11 +3131,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3126,11 +3153,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3148,11 +3175,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3170,11 +3197,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3192,11 +3219,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3214,11 +3241,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3236,11 +3263,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3258,11 +3285,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3280,11 +3307,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3302,11 +3329,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3324,11 +3351,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3346,11 +3373,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3368,11 +3395,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3390,11 +3417,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3412,11 +3439,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3434,11 +3461,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3456,11 +3483,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3478,11 +3505,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3500,11 +3527,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3522,11 +3549,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3544,11 +3571,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3566,11 +3593,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3588,11 +3615,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3610,11 +3637,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3632,11 +3659,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3654,11 +3681,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3676,11 +3703,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3698,11 +3725,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3720,11 +3747,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3742,11 +3769,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3764,11 +3791,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3786,11 +3813,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3808,11 +3835,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3830,11 +3857,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3852,11 +3879,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3874,11 +3901,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3896,11 +3923,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3918,11 +3945,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3940,11 +3967,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3962,11 +3989,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3984,11 +4011,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4006,11 +4033,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4028,11 +4055,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4050,11 +4077,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4072,11 +4099,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4094,11 +4121,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4116,11 +4143,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4138,11 +4165,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4160,11 +4187,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4182,11 +4209,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4204,11 +4231,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4226,11 +4253,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4248,11 +4275,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4270,11 +4297,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4292,11 +4319,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4314,11 +4341,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4336,11 +4363,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4358,11 +4385,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4380,11 +4407,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4402,11 +4429,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4424,11 +4451,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4446,11 +4473,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4468,11 +4495,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4490,11 +4517,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4512,11 +4539,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4534,11 +4561,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4556,11 +4583,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4578,11 +4605,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4600,11 +4627,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4622,11 +4649,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4644,11 +4671,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4666,11 +4693,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4688,11 +4715,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4710,11 +4737,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4732,11 +4759,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4754,11 +4781,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4776,11 +4803,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4798,11 +4825,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4820,11 +4847,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4842,11 +4869,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4864,11 +4891,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4886,11 +4913,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4908,11 +4935,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4930,11 +4957,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4952,11 +4979,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4974,11 +5001,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4996,11 +5023,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5018,11 +5045,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5040,11 +5067,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5062,11 +5089,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5084,11 +5111,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5106,11 +5133,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5128,11 +5155,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5150,11 +5177,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5172,11 +5199,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5194,11 +5221,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5216,11 +5243,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5238,11 +5265,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5260,11 +5287,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5282,11 +5309,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5304,11 +5331,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5326,11 +5353,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5348,11 +5375,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5370,11 +5397,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5392,11 +5419,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5414,11 +5441,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5436,11 +5463,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5458,11 +5485,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5480,11 +5507,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5502,11 +5529,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5524,11 +5551,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5546,11 +5573,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5568,11 +5595,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5590,11 +5617,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5612,11 +5639,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5634,11 +5661,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5656,11 +5683,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5678,11 +5705,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5700,11 +5727,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5722,11 +5749,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5744,11 +5771,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5766,11 +5793,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5788,11 +5815,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5810,11 +5837,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5832,11 +5859,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5854,11 +5881,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5876,11 +5903,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5898,11 +5925,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5920,11 +5947,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5942,11 +5969,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5964,11 +5991,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5986,11 +6013,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6008,11 +6035,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6030,11 +6057,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6052,11 +6079,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6074,11 +6101,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6096,11 +6123,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6118,11 +6145,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6140,11 +6167,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6162,11 +6189,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6184,11 +6211,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6206,11 +6233,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6228,11 +6255,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6250,11 +6277,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6272,11 +6299,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6294,11 +6321,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6316,11 +6343,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6338,11 +6365,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6360,11 +6387,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6382,11 +6409,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6404,11 +6431,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6426,11 +6453,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6448,11 +6475,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6470,11 +6497,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6492,11 +6519,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6514,11 +6541,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6536,11 +6563,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6558,11 +6585,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6580,11 +6607,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6602,11 +6629,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6624,11 +6651,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6646,11 +6673,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6668,11 +6695,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6690,11 +6717,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6712,11 +6739,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6734,11 +6761,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6756,11 +6783,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6778,11 +6805,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6800,11 +6827,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6822,11 +6849,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6844,11 +6871,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6866,11 +6893,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6888,11 +6915,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6910,11 +6937,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6932,11 +6959,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6954,11 +6981,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6976,11 +7003,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6998,11 +7025,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7020,11 +7047,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7042,11 +7069,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7064,11 +7091,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7086,11 +7113,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7108,11 +7135,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7130,11 +7157,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7152,11 +7179,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7174,11 +7201,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7196,11 +7223,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7218,11 +7245,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7240,11 +7267,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7262,11 +7289,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7284,11 +7311,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7306,11 +7333,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7328,11 +7355,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7350,11 +7377,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7372,11 +7399,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7394,11 +7421,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7416,11 +7443,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7438,11 +7465,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7460,11 +7487,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7482,11 +7509,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7504,11 +7531,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7526,11 +7553,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7548,11 +7575,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7570,11 +7597,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7592,11 +7619,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7614,11 +7641,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7636,11 +7663,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7658,11 +7685,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7680,11 +7707,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7702,11 +7729,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7724,11 +7751,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7746,11 +7773,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7768,11 +7795,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7790,11 +7817,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7812,11 +7839,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7834,11 +7861,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7856,11 +7883,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7878,11 +7905,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7900,11 +7927,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7922,11 +7949,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7944,11 +7971,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7966,11 +7993,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7988,11 +8015,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8010,11 +8037,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8032,11 +8059,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8054,11 +8081,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8076,11 +8103,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8098,11 +8125,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8120,11 +8147,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8142,11 +8169,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8164,11 +8191,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8186,11 +8213,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8208,11 +8235,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8230,11 +8257,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8252,11 +8279,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8274,11 +8301,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8296,11 +8323,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8318,11 +8345,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8340,11 +8367,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8362,11 +8389,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8384,11 +8411,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8406,11 +8433,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8428,11 +8455,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8450,11 +8477,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8472,11 +8499,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8494,11 +8521,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8516,11 +8543,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8538,11 +8565,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8560,11 +8587,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8582,11 +8609,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8604,11 +8631,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8626,11 +8653,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8648,11 +8675,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8670,11 +8697,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8692,11 +8719,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8714,11 +8741,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8736,11 +8763,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8758,11 +8785,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8780,11 +8807,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8802,11 +8829,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8824,11 +8851,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8846,11 +8873,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8868,11 +8895,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8890,11 +8917,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8912,11 +8939,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8934,11 +8961,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8956,11 +8983,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8978,11 +9005,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9000,11 +9027,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9022,11 +9049,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9044,11 +9071,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9066,11 +9093,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9088,11 +9115,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9110,11 +9137,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9132,11 +9159,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9154,11 +9181,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9176,11 +9203,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9198,11 +9225,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9220,11 +9247,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9242,11 +9269,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9264,11 +9291,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9286,11 +9313,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9308,11 +9335,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9330,11 +9357,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9352,11 +9379,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9374,11 +9401,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9396,11 +9423,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9418,11 +9445,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9440,11 +9467,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9462,11 +9489,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9484,11 +9511,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9506,11 +9533,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9528,11 +9555,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9550,11 +9577,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9572,11 +9599,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9594,11 +9621,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9616,11 +9643,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9638,11 +9665,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9660,11 +9687,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9682,11 +9709,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9704,11 +9731,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9726,11 +9753,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9748,11 +9775,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9770,11 +9797,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9792,11 +9819,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9814,11 +9841,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9836,11 +9863,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9858,11 +9885,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9880,11 +9907,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9902,11 +9929,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9924,11 +9951,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9946,11 +9973,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="21">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9968,11 +9995,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9990,11 +10017,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10012,11 +10039,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10034,11 +10061,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10056,11 +10083,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10078,11 +10105,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10100,11 +10127,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10122,11 +10149,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10144,11 +10171,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10166,11 +10193,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10188,11 +10215,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/Project File.xlsx
+++ b/Project File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Siddharth's File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D95596-BA82-4645-8C7C-90617863D746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814D3455-4307-4347-A52F-3B0369D00748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>Met an old friend.</t>
+  </si>
+  <si>
+    <t>Started studying networking.</t>
+  </si>
+  <si>
+    <t>Practiced few questions on Cisco Packet Tracer.</t>
   </si>
 </sst>
 </file>
@@ -1934,48 +1940,96 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+      <c r="A25" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B25" s="14">
+        <v>600</v>
+      </c>
+      <c r="C25" s="14">
+        <v>45</v>
+      </c>
+      <c r="D25" s="14">
+        <v>375</v>
+      </c>
+      <c r="E25" s="14">
+        <v>120</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>300</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" ref="I25:I26" si="10">IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
+        <v>1440</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" ref="J25:J26" si="11">IF(I25="","",1440-I25)</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B26" s="14">
+        <v>600</v>
+      </c>
+      <c r="C26" s="14">
+        <v>45</v>
+      </c>
+      <c r="D26" s="14">
+        <v>350</v>
+      </c>
+      <c r="E26" s="14">
+        <v>120</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>325</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" si="10"/>
+        <v>1440</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
@@ -2933,11 +2987,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="12">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="13">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2955,11 +3009,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2977,11 +3031,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2999,11 +3053,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3021,11 +3075,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3043,11 +3097,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3065,11 +3119,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3087,11 +3141,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3109,11 +3163,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3131,11 +3185,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3153,11 +3207,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3175,11 +3229,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3197,11 +3251,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3219,11 +3273,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3241,11 +3295,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3263,11 +3317,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3285,11 +3339,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3307,11 +3361,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3329,11 +3383,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3351,11 +3405,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3373,11 +3427,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3395,11 +3449,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3417,11 +3471,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3439,11 +3493,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3461,11 +3515,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3483,11 +3537,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3505,11 +3559,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3527,11 +3581,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3549,11 +3603,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3571,11 +3625,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3593,11 +3647,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3615,11 +3669,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3637,11 +3691,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3659,11 +3713,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3681,11 +3735,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3703,11 +3757,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3725,11 +3779,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3747,11 +3801,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3769,11 +3823,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3791,11 +3845,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3813,11 +3867,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3835,11 +3889,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3857,11 +3911,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3879,11 +3933,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3901,11 +3955,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3923,11 +3977,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3945,11 +3999,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3967,11 +4021,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3989,11 +4043,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4011,11 +4065,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4033,11 +4087,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4055,11 +4109,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4077,11 +4131,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4099,11 +4153,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4121,11 +4175,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4143,11 +4197,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4165,11 +4219,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4187,11 +4241,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4209,11 +4263,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4231,11 +4285,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4253,11 +4307,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4275,11 +4329,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4297,11 +4351,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4319,11 +4373,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4341,11 +4395,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="14">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="15">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4363,11 +4417,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4385,11 +4439,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4407,11 +4461,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4429,11 +4483,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4451,11 +4505,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4473,11 +4527,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4495,11 +4549,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4517,11 +4571,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4539,11 +4593,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4561,11 +4615,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4583,11 +4637,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4605,11 +4659,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4627,11 +4681,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4649,11 +4703,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4671,11 +4725,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4693,11 +4747,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4715,11 +4769,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4737,11 +4791,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4759,11 +4813,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4781,11 +4835,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4803,11 +4857,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4825,11 +4879,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4847,11 +4901,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4869,11 +4923,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4891,11 +4945,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4913,11 +4967,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4935,11 +4989,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4957,11 +5011,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4979,11 +5033,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5001,11 +5055,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5023,11 +5077,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5045,11 +5099,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5067,11 +5121,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5089,11 +5143,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5111,11 +5165,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5133,11 +5187,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5155,11 +5209,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5177,11 +5231,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5199,11 +5253,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5221,11 +5275,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5243,11 +5297,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5265,11 +5319,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5287,11 +5341,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5309,11 +5363,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5331,11 +5385,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5353,11 +5407,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5375,11 +5429,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5397,11 +5451,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5419,11 +5473,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5441,11 +5495,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5463,11 +5517,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5485,11 +5539,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5507,11 +5561,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5529,11 +5583,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5551,11 +5605,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5573,11 +5627,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5595,11 +5649,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5617,11 +5671,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5639,11 +5693,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5661,11 +5715,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5683,11 +5737,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5705,11 +5759,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5727,11 +5781,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5749,11 +5803,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="16">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="17">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5771,11 +5825,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5793,11 +5847,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5815,11 +5869,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5837,11 +5891,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5859,11 +5913,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5881,11 +5935,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5903,11 +5957,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5925,11 +5979,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5947,11 +6001,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5969,11 +6023,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5991,11 +6045,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6013,11 +6067,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6035,11 +6089,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6057,11 +6111,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6079,11 +6133,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6101,11 +6155,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6123,11 +6177,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6145,11 +6199,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6167,11 +6221,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6189,11 +6243,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6211,11 +6265,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6233,11 +6287,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6255,11 +6309,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6277,11 +6331,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6299,11 +6353,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6321,11 +6375,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6343,11 +6397,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6365,11 +6419,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6387,11 +6441,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6409,11 +6463,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6431,11 +6485,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6453,11 +6507,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6475,11 +6529,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6497,11 +6551,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6519,11 +6573,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6541,11 +6595,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6563,11 +6617,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6585,11 +6639,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6607,11 +6661,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6629,11 +6683,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6651,11 +6705,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6673,11 +6727,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6695,11 +6749,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6717,11 +6771,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6739,11 +6793,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6761,11 +6815,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6783,11 +6837,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6805,11 +6859,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6827,11 +6881,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6849,11 +6903,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6871,11 +6925,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6893,11 +6947,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6915,11 +6969,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6937,11 +6991,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6959,11 +7013,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6981,11 +7035,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7003,11 +7057,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7025,11 +7079,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7047,11 +7101,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7069,11 +7123,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7091,11 +7145,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7113,11 +7167,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7135,11 +7189,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7157,11 +7211,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="18">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="19">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7179,11 +7233,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7201,11 +7255,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7223,11 +7277,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7245,11 +7299,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7267,11 +7321,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7289,11 +7343,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7311,11 +7365,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7333,11 +7387,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7355,11 +7409,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7377,11 +7431,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7399,11 +7453,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7421,11 +7475,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7443,11 +7497,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7465,11 +7519,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7487,11 +7541,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7509,11 +7563,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7531,11 +7585,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7553,11 +7607,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7575,11 +7629,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7597,11 +7651,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7619,11 +7673,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7641,11 +7695,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7663,11 +7717,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7685,11 +7739,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7707,11 +7761,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7729,11 +7783,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7751,11 +7805,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7773,11 +7827,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7795,11 +7849,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7817,11 +7871,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7839,11 +7893,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7861,11 +7915,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7883,11 +7937,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7905,11 +7959,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7927,11 +7981,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7949,11 +8003,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7971,11 +8025,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7993,11 +8047,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8015,11 +8069,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8037,11 +8091,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8059,11 +8113,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8081,11 +8135,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8103,11 +8157,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8125,11 +8179,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8147,11 +8201,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8169,11 +8223,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8191,11 +8245,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8213,11 +8267,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8235,11 +8289,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8257,11 +8311,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8279,11 +8333,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8301,11 +8355,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8323,11 +8377,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8345,11 +8399,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8367,11 +8421,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8389,11 +8443,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8411,11 +8465,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8433,11 +8487,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8455,11 +8509,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8477,11 +8531,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8499,11 +8553,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8521,11 +8575,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8543,11 +8597,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8565,11 +8619,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="20">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="21">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8587,11 +8641,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8609,11 +8663,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8631,11 +8685,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8653,11 +8707,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8675,11 +8729,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8697,11 +8751,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8719,11 +8773,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8741,11 +8795,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8763,11 +8817,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8785,11 +8839,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8807,11 +8861,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8829,11 +8883,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8851,11 +8905,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8873,11 +8927,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8895,11 +8949,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8917,11 +8971,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8939,11 +8993,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8961,11 +9015,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8983,11 +9037,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9005,11 +9059,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9027,11 +9081,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9049,11 +9103,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9071,11 +9125,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9093,11 +9147,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9115,11 +9169,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9137,11 +9191,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9159,11 +9213,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9181,11 +9235,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9203,11 +9257,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9225,11 +9279,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9247,11 +9301,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9269,11 +9323,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9291,11 +9345,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9313,11 +9367,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9335,11 +9389,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9357,11 +9411,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9379,11 +9433,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9401,11 +9455,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9423,11 +9477,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9445,11 +9499,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9467,11 +9521,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9489,11 +9543,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9511,11 +9565,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9533,11 +9587,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9555,11 +9609,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9577,11 +9631,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9599,11 +9653,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9621,11 +9675,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9643,11 +9697,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9665,11 +9719,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9687,11 +9741,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9709,11 +9763,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9731,11 +9785,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9753,11 +9807,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9775,11 +9829,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9797,11 +9851,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9819,11 +9873,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9841,11 +9895,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9863,11 +9917,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9885,11 +9939,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9907,11 +9961,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9929,11 +9983,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9951,11 +10005,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9973,11 +10027,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="22">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="21">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="23">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9995,11 +10049,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10017,11 +10071,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10039,11 +10093,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10061,11 +10115,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10083,11 +10137,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10105,11 +10159,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10127,11 +10181,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10149,11 +10203,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10171,11 +10225,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10193,11 +10247,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10215,11 +10269,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
